--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.3916569054014</v>
+        <v>8.188644247127728</v>
       </c>
       <c r="D2" t="n">
-        <v>50.45059189631872</v>
+        <v>8.198221183151793</v>
       </c>
       <c r="E2" t="n">
-        <v>21.93957097232021</v>
+        <v>3.565180283002035</v>
       </c>
       <c r="F2" t="n">
-        <v>21.85957258401067</v>
+        <v>3.552180544901735</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.99242145577021</v>
+        <v>10.88626848656266</v>
       </c>
       <c r="D3" t="n">
-        <v>66.5384362215531</v>
+        <v>10.81249588600238</v>
       </c>
       <c r="E3" t="n">
-        <v>21.93957097232021</v>
+        <v>3.565180283002035</v>
       </c>
       <c r="F3" t="n">
-        <v>21.85957258401067</v>
+        <v>3.552180544901735</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.17552729470419</v>
+        <v>7.666023185389431</v>
       </c>
       <c r="D4" t="n">
-        <v>46.72239207900532</v>
+        <v>7.592388712838366</v>
       </c>
       <c r="E4" t="n">
-        <v>21.93957097232021</v>
+        <v>3.565180283002035</v>
       </c>
       <c r="F4" t="n">
-        <v>21.85957258401067</v>
+        <v>3.552180544901735</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.255353540489948</v>
+        <v>1.178994950329617</v>
       </c>
       <c r="D5" t="n">
-        <v>7.107284629849052</v>
+        <v>1.154933752350471</v>
       </c>
       <c r="E5" t="n">
-        <v>21.93957097232021</v>
+        <v>3.565180283002035</v>
       </c>
       <c r="F5" t="n">
-        <v>21.85957258401067</v>
+        <v>3.552180544901735</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
